--- a/Data point Supporting files/Germany 2022/Reserves.xlsx
+++ b/Data point Supporting files/Germany 2022/Reserves.xlsx
@@ -5,7 +5,7 @@
   <workbookPr backupFile="false" showObjects="all" date1904="false"/>
   <workbookProtection/>
   <bookViews>
-    <workbookView showHorizontalScroll="true" showVerticalScroll="true" showSheetTabs="true" xWindow="0" yWindow="0" windowWidth="16384" windowHeight="8192" tabRatio="500" firstSheet="0" activeTab="1"/>
+    <workbookView showHorizontalScroll="true" showVerticalScroll="true" showSheetTabs="true" xWindow="0" yWindow="0" windowWidth="16384" windowHeight="8192" tabRatio="500" firstSheet="0" activeTab="24"/>
   </bookViews>
   <sheets>
     <sheet name="Aluminium" sheetId="1" state="visible" r:id="rId2"/>
@@ -54,7 +54,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="759" uniqueCount="147">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="761" uniqueCount="147">
   <si>
     <t xml:space="preserve">Country</t>
   </si>
@@ -576,7 +576,7 @@
     <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
   </cellStyleXfs>
-  <cellXfs count="4">
+  <cellXfs count="3">
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
@@ -586,10 +586,6 @@
       <protection locked="true" hidden="false"/>
     </xf>
     <xf numFmtId="164" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -750,61 +746,61 @@
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
   <dimension ref="A1:B7"/>
-  <sheetFormatPr defaultColWidth="10.5390625" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <sheetFormatPr defaultColWidth="10.54296875" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <sheetData>
     <row r="1" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A1" s="0" t="s">
+      <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="0" t="s">
+      <c r="B1" s="1" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A2" s="0" t="s">
+      <c r="A2" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="B2" s="0" t="n">
+      <c r="B2" s="1" t="n">
         <v>450</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A3" s="0" t="s">
+      <c r="A3" s="1" t="s">
         <v>18</v>
       </c>
-      <c r="B3" s="0" t="n">
+      <c r="B3" s="1" t="n">
         <v>560</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A4" s="0" t="s">
+      <c r="A4" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="B4" s="0" t="n">
+      <c r="B4" s="1" t="n">
         <v>10000</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A5" s="0" t="s">
+      <c r="A5" s="1" t="s">
         <v>26</v>
       </c>
-      <c r="B5" s="0" t="n">
+      <c r="B5" s="1" t="n">
         <v>580</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A6" s="0" t="s">
+      <c r="A6" s="1" t="s">
         <v>11</v>
       </c>
-      <c r="B6" s="0" t="n">
+      <c r="B6" s="1" t="n">
         <v>250</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A7" s="0" t="s">
+      <c r="A7" s="1" t="s">
         <v>25</v>
       </c>
-      <c r="B7" s="0" t="n">
+      <c r="B7" s="1" t="n">
         <f aca="false">SUM(B2:B6)</f>
         <v>11840</v>
       </c>
@@ -2611,7 +2607,7 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:B2"/>
+  <dimension ref="A1:B3"/>
   <sheetFormatPr defaultColWidth="8.54296875" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <sheetData>
     <row r="1" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -2627,6 +2623,14 @@
         <v>5</v>
       </c>
       <c r="B2" s="1" t="n">
+        <v>16000000</v>
+      </c>
+    </row>
+    <row r="3" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A3" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="B3" s="1" t="n">
         <v>16000000</v>
       </c>
     </row>
@@ -2646,7 +2650,7 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:B4"/>
+  <dimension ref="A1:B5"/>
   <sheetFormatPr defaultColWidth="8.54296875" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <sheetData>
     <row r="1" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -2679,6 +2683,14 @@
       </c>
       <c r="B4" s="1" t="n">
         <v>180000</v>
+      </c>
+    </row>
+    <row r="5" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A5" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="B5" s="0" t="n">
+        <v>319000</v>
       </c>
     </row>
   </sheetData>
@@ -3348,10 +3360,10 @@
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
   <dimension ref="A1:B106"/>
-  <sheetFormatPr defaultColWidth="8.5390625" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <sheetFormatPr defaultColWidth="8.54296875" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="32"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="0" width="20"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="32"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="1" width="20"/>
   </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -3363,834 +3375,834 @@
       </c>
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A2" s="0" t="s">
+      <c r="A2" s="1" t="s">
         <v>74</v>
       </c>
-      <c r="B2" s="0" t="n">
+      <c r="B2" s="1" t="n">
         <v>12000000</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A3" s="0" t="s">
+      <c r="A3" s="1" t="s">
         <v>75</v>
       </c>
-      <c r="B3" s="0" t="n">
+      <c r="B3" s="1" t="n">
         <v>27000000</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A4" s="0" t="s">
+      <c r="A4" s="1" t="s">
         <v>64</v>
       </c>
-      <c r="B4" s="0" t="n">
+      <c r="B4" s="1" t="n">
         <v>1660000000</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A5" s="0" t="s">
+      <c r="A5" s="1" t="s">
         <v>76</v>
       </c>
-      <c r="B5" s="0" t="n">
+      <c r="B5" s="1" t="n">
         <v>347000000</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A6" s="0" t="s">
+      <c r="A6" s="1" t="s">
         <v>54</v>
       </c>
-      <c r="B6" s="0" t="n">
+      <c r="B6" s="1" t="n">
         <v>386000000</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A7" s="0" t="s">
+      <c r="A7" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="B7" s="0" t="n">
+      <c r="B7" s="1" t="n">
         <v>202000000</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A8" s="0" t="s">
+      <c r="A8" s="1" t="s">
         <v>57</v>
       </c>
-      <c r="B8" s="0" t="n">
+      <c r="B8" s="1" t="n">
         <v>5000000</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A9" s="0" t="s">
+      <c r="A9" s="1" t="s">
         <v>77</v>
       </c>
-      <c r="B9" s="0" t="n">
+      <c r="B9" s="1" t="n">
         <v>952000000</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A10" s="0" t="s">
+      <c r="A10" s="1" t="s">
         <v>78</v>
       </c>
-      <c r="B10" s="0" t="n">
+      <c r="B10" s="1" t="n">
         <v>23000000</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A11" s="0" t="s">
+      <c r="A11" s="1" t="s">
         <v>79</v>
       </c>
-      <c r="B11" s="0" t="n">
+      <c r="B11" s="1" t="n">
         <v>4000000</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A12" s="0" t="s">
+      <c r="A12" s="1" t="s">
         <v>80</v>
       </c>
-      <c r="B12" s="0" t="n">
+      <c r="B12" s="1" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A13" s="0" t="s">
+      <c r="A13" s="1" t="s">
         <v>81</v>
       </c>
-      <c r="B13" s="0" t="n">
+      <c r="B13" s="1" t="n">
         <v>27000000</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A14" s="0" t="s">
+      <c r="A14" s="1" t="s">
         <v>82</v>
       </c>
-      <c r="B14" s="0" t="n">
+      <c r="B14" s="1" t="n">
         <v>1000000</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A15" s="0" t="s">
+      <c r="A15" s="1" t="s">
         <v>83</v>
       </c>
-      <c r="B15" s="0" t="n">
+      <c r="B15" s="1" t="n">
         <v>1000000</v>
       </c>
     </row>
     <row r="16" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A16" s="0" t="s">
+      <c r="A16" s="1" t="s">
         <v>16</v>
       </c>
-      <c r="B16" s="0" t="n">
+      <c r="B16" s="1" t="n">
         <v>33000000</v>
       </c>
     </row>
     <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A17" s="0" t="s">
+      <c r="A17" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="B17" s="0" t="n">
+      <c r="B17" s="1" t="n">
         <v>2021000000</v>
       </c>
     </row>
     <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A18" s="0" t="s">
+      <c r="A18" s="1" t="s">
         <v>84</v>
       </c>
-      <c r="B18" s="0" t="n">
+      <c r="B18" s="1" t="n">
         <v>150000000</v>
       </c>
     </row>
     <row r="19" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A19" s="0" t="s">
+      <c r="A19" s="1" t="s">
         <v>85</v>
       </c>
-      <c r="B19" s="0" t="n">
+      <c r="B19" s="1" t="n">
         <v>2000000</v>
       </c>
     </row>
     <row r="20" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A20" s="0" t="s">
+      <c r="A20" s="1" t="s">
         <v>86</v>
       </c>
-      <c r="B20" s="0" t="n">
+      <c r="B20" s="1" t="n">
         <v>27000000</v>
       </c>
     </row>
     <row r="21" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A21" s="0" t="s">
+      <c r="A21" s="1" t="s">
         <v>18</v>
       </c>
-      <c r="B21" s="0" t="n">
+      <c r="B21" s="1" t="n">
         <v>25958000000</v>
       </c>
     </row>
     <row r="22" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A22" s="0" t="s">
+      <c r="A22" s="1" t="s">
         <v>87</v>
       </c>
-      <c r="B22" s="0" t="n">
+      <c r="B22" s="1" t="n">
         <v>204000000</v>
       </c>
     </row>
     <row r="23" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A23" s="0" t="s">
+      <c r="A23" s="1" t="s">
         <v>36</v>
       </c>
-      <c r="B23" s="0" t="n">
+      <c r="B23" s="1" t="n">
         <v>20000000</v>
       </c>
     </row>
     <row r="24" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A24" s="0" t="s">
+      <c r="A24" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="B24" s="0" t="n">
+      <c r="B24" s="1" t="n">
         <v>3690000000</v>
       </c>
     </row>
     <row r="25" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A25" s="0" t="s">
+      <c r="A25" s="1" t="s">
         <v>39</v>
       </c>
-      <c r="B25" s="0" t="n">
+      <c r="B25" s="1" t="n">
         <v>278000000</v>
       </c>
     </row>
     <row r="26" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A26" s="0" t="s">
+      <c r="A26" s="1" t="s">
         <v>88</v>
       </c>
-      <c r="B26" s="0" t="n">
+      <c r="B26" s="1" t="n">
         <v>10000000</v>
       </c>
     </row>
     <row r="27" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A27" s="0" t="s">
+      <c r="A27" s="1" t="s">
         <v>31</v>
       </c>
-      <c r="B27" s="0" t="n">
+      <c r="B27" s="1" t="n">
         <v>17000000</v>
       </c>
     </row>
     <row r="28" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A28" s="0" t="s">
+      <c r="A28" s="1" t="s">
         <v>89</v>
       </c>
-      <c r="B28" s="0" t="n">
+      <c r="B28" s="1" t="n">
         <v>1000000</v>
       </c>
     </row>
     <row r="29" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A29" s="0" t="s">
+      <c r="A29" s="1" t="s">
         <v>30</v>
       </c>
-      <c r="B29" s="0" t="n">
+      <c r="B29" s="1" t="n">
         <v>24000000</v>
       </c>
     </row>
     <row r="30" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A30" s="0" t="s">
+      <c r="A30" s="1" t="s">
         <v>90</v>
       </c>
-      <c r="B30" s="0" t="n">
+      <c r="B30" s="1" t="n">
         <v>46000000</v>
       </c>
     </row>
     <row r="31" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A31" s="0" t="s">
+      <c r="A31" s="1" t="s">
         <v>91</v>
       </c>
-      <c r="B31" s="0" t="n">
+      <c r="B31" s="1" t="n">
         <v>1126000000</v>
       </c>
     </row>
     <row r="32" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A32" s="0" t="s">
+      <c r="A32" s="1" t="s">
         <v>65</v>
       </c>
-      <c r="B32" s="0" t="n">
+      <c r="B32" s="1" t="n">
         <v>449000000</v>
       </c>
     </row>
     <row r="33" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A33" s="0" t="s">
+      <c r="A33" s="1" t="s">
         <v>92</v>
       </c>
-      <c r="B33" s="0" t="n">
+      <c r="B33" s="1" t="n">
         <v>150000000</v>
       </c>
     </row>
     <row r="34" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A34" s="0" t="s">
+      <c r="A34" s="1" t="s">
         <v>93</v>
       </c>
-      <c r="B34" s="0" t="n">
+      <c r="B34" s="1" t="n">
         <v>172000000</v>
       </c>
     </row>
     <row r="35" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A35" s="0" t="s">
+      <c r="A35" s="1" t="s">
         <v>94</v>
       </c>
-      <c r="B35" s="0" t="n">
+      <c r="B35" s="1" t="n">
         <v>11000000</v>
       </c>
     </row>
     <row r="36" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A36" s="0" t="s">
+      <c r="A36" s="1" t="s">
         <v>61</v>
       </c>
-      <c r="B36" s="0" t="n">
+      <c r="B36" s="1" t="n">
         <v>272000000</v>
       </c>
     </row>
     <row r="37" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A37" s="0" t="s">
+      <c r="A37" s="1" t="s">
         <v>95</v>
       </c>
-      <c r="B37" s="0" t="n">
+      <c r="B37" s="1" t="n">
         <v>5000000</v>
       </c>
     </row>
     <row r="38" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A38" s="0" t="s">
+      <c r="A38" s="1" t="s">
         <v>96</v>
       </c>
-      <c r="B38" s="0" t="n">
+      <c r="B38" s="1" t="n">
         <v>15000000</v>
       </c>
     </row>
     <row r="39" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A39" s="0" t="s">
+      <c r="A39" s="1" t="s">
         <v>40</v>
       </c>
-      <c r="B39" s="0" t="n">
+      <c r="B39" s="1" t="n">
         <v>90000000</v>
       </c>
     </row>
     <row r="40" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A40" s="0" t="s">
+      <c r="A40" s="1" t="s">
         <v>58</v>
       </c>
-      <c r="B40" s="0" t="n">
+      <c r="B40" s="1" t="n">
         <v>1000000</v>
       </c>
     </row>
     <row r="41" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A41" s="0" t="s">
+      <c r="A41" s="1" t="s">
         <v>97</v>
       </c>
-      <c r="B41" s="0" t="n">
+      <c r="B41" s="1" t="n">
         <v>11000000</v>
       </c>
     </row>
     <row r="42" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A42" s="3" t="s">
+      <c r="A42" s="1" t="s">
         <v>98</v>
       </c>
-      <c r="B42" s="3" t="n">
+      <c r="B42" s="1" t="n">
         <v>1497000000</v>
       </c>
     </row>
     <row r="43" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A43" s="0" t="s">
+      <c r="A43" s="1" t="s">
         <v>99</v>
       </c>
-      <c r="B43" s="0" t="n">
+      <c r="B43" s="1" t="n">
         <v>2000000</v>
       </c>
     </row>
     <row r="44" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A44" s="0" t="s">
+      <c r="A44" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="B44" s="0" t="n">
+      <c r="B44" s="1" t="n">
         <v>595000000</v>
       </c>
     </row>
     <row r="45" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A45" s="0" t="s">
+      <c r="A45" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="B45" s="0" t="n">
+      <c r="B45" s="1" t="n">
         <v>309000000</v>
       </c>
     </row>
     <row r="46" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A46" s="0" t="s">
+      <c r="A46" s="1" t="s">
         <v>50</v>
       </c>
-      <c r="B46" s="0" t="n">
+      <c r="B46" s="1" t="n">
         <v>28380000000</v>
       </c>
     </row>
     <row r="47" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A47" s="0" t="s">
+      <c r="A47" s="1" t="s">
         <v>100</v>
       </c>
-      <c r="B47" s="0" t="n">
+      <c r="B47" s="1" t="n">
         <v>19730000000</v>
       </c>
     </row>
     <row r="48" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A48" s="0" t="s">
+      <c r="A48" s="1" t="s">
         <v>66</v>
       </c>
-      <c r="B48" s="0" t="n">
+      <c r="B48" s="1" t="n">
         <v>2000000</v>
       </c>
     </row>
     <row r="49" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A49" s="0" t="s">
+      <c r="A49" s="1" t="s">
         <v>101</v>
       </c>
-      <c r="B49" s="0" t="n">
+      <c r="B49" s="1" t="n">
         <v>79000000</v>
       </c>
     </row>
     <row r="50" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A50" s="0" t="s">
+      <c r="A50" s="1" t="s">
         <v>102</v>
       </c>
-      <c r="B50" s="0" t="n">
+      <c r="B50" s="1" t="n">
         <v>14000000</v>
       </c>
     </row>
     <row r="51" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A51" s="0" t="s">
+      <c r="A51" s="1" t="s">
         <v>103</v>
       </c>
-      <c r="B51" s="0" t="n">
+      <c r="B51" s="1" t="n">
         <v>6000000</v>
       </c>
     </row>
     <row r="52" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A52" s="0" t="s">
+      <c r="A52" s="1" t="s">
         <v>67</v>
       </c>
-      <c r="B52" s="0" t="n">
+      <c r="B52" s="1" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="53" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A53" s="0" t="s">
+      <c r="A53" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="B53" s="0" t="n">
+      <c r="B53" s="1" t="n">
         <v>4081000000</v>
       </c>
     </row>
     <row r="54" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A54" s="0" t="s">
+      <c r="A54" s="1" t="s">
         <v>104</v>
       </c>
-      <c r="B54" s="0" t="n">
+      <c r="B54" s="1" t="n">
         <v>13810000000</v>
       </c>
     </row>
     <row r="55" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A55" s="0" t="s">
+      <c r="A55" s="1" t="s">
         <v>19</v>
       </c>
-      <c r="B55" s="0" t="n">
+      <c r="B55" s="1" t="n">
         <v>5000000</v>
       </c>
     </row>
     <row r="56" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A56" s="0" t="s">
+      <c r="A56" s="1" t="s">
         <v>105</v>
       </c>
-      <c r="B56" s="0" t="n">
+      <c r="B56" s="1" t="n">
         <v>6580000000</v>
       </c>
     </row>
     <row r="57" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A57" s="0" t="s">
+      <c r="A57" s="1" t="s">
         <v>106</v>
       </c>
-      <c r="B57" s="0" t="n">
+      <c r="B57" s="1" t="n">
         <v>2000000</v>
       </c>
     </row>
     <row r="58" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A58" s="0" t="s">
+      <c r="A58" s="1" t="s">
         <v>107</v>
       </c>
-      <c r="B58" s="0" t="n">
+      <c r="B58" s="1" t="n">
         <v>490000000</v>
       </c>
     </row>
     <row r="59" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A59" s="0" t="s">
+      <c r="A59" s="1" t="s">
         <v>51</v>
       </c>
-      <c r="B59" s="0" t="n">
+      <c r="B59" s="1" t="n">
         <v>3000000</v>
       </c>
     </row>
     <row r="60" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A60" s="0" t="s">
+      <c r="A60" s="1" t="s">
         <v>20</v>
       </c>
-      <c r="B60" s="0" t="n">
+      <c r="B60" s="1" t="n">
         <v>756000000</v>
       </c>
     </row>
     <row r="61" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A61" s="0" t="s">
+      <c r="A61" s="1" t="s">
         <v>108</v>
       </c>
-      <c r="B61" s="0" t="n">
+      <c r="B61" s="1" t="n">
         <v>43000000</v>
       </c>
     </row>
     <row r="62" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A62" s="0" t="s">
+      <c r="A62" s="1" t="s">
         <v>33</v>
       </c>
-      <c r="B62" s="0" t="n">
+      <c r="B62" s="1" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="63" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A63" s="0" t="s">
+      <c r="A63" s="1" t="s">
         <v>109</v>
       </c>
-      <c r="B63" s="0" t="n">
+      <c r="B63" s="1" t="n">
         <v>19000000</v>
       </c>
     </row>
     <row r="64" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A64" s="0" t="s">
+      <c r="A64" s="1" t="s">
         <v>110</v>
       </c>
-      <c r="B64" s="0" t="n">
+      <c r="B64" s="1" t="n">
         <v>9000000</v>
       </c>
     </row>
     <row r="65" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A65" s="0" t="s">
+      <c r="A65" s="1" t="s">
         <v>111</v>
       </c>
-      <c r="B65" s="0" t="n">
+      <c r="B65" s="1" t="n">
         <v>8000000</v>
       </c>
     </row>
     <row r="66" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A66" s="0" t="s">
+      <c r="A66" s="1" t="s">
         <v>112</v>
       </c>
-      <c r="B66" s="0" t="n">
+      <c r="B66" s="1" t="n">
         <v>20000000</v>
       </c>
     </row>
     <row r="67" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A67" s="0" t="s">
+      <c r="A67" s="1" t="s">
         <v>113</v>
       </c>
-      <c r="B67" s="0" t="n">
+      <c r="B67" s="1" t="n">
         <v>5030000000</v>
       </c>
     </row>
     <row r="68" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A68" s="0" t="s">
+      <c r="A68" s="1" t="s">
         <v>48</v>
       </c>
-      <c r="B68" s="0" t="n">
+      <c r="B68" s="1" t="n">
         <v>934000000</v>
       </c>
     </row>
     <row r="69" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A69" s="0" t="s">
+      <c r="A69" s="1" t="s">
         <v>114</v>
       </c>
-      <c r="B69" s="0" t="n">
+      <c r="B69" s="1" t="n">
         <v>731000000</v>
       </c>
     </row>
     <row r="70" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A70" s="0" t="s">
+      <c r="A70" s="1" t="s">
         <v>21</v>
       </c>
-      <c r="B70" s="0" t="n">
+      <c r="B70" s="1" t="n">
         <v>73000000</v>
       </c>
     </row>
     <row r="71" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A71" s="0" t="s">
+      <c r="A71" s="1" t="s">
         <v>34</v>
       </c>
-      <c r="B71" s="0" t="n">
+      <c r="B71" s="1" t="n">
         <v>20000000</v>
       </c>
     </row>
     <row r="72" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A72" s="0" t="s">
+      <c r="A72" s="1" t="s">
         <v>26</v>
       </c>
-      <c r="B72" s="0" t="n">
+      <c r="B72" s="1" t="n">
         <v>117000000</v>
       </c>
     </row>
     <row r="73" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A73" s="0" t="s">
+      <c r="A73" s="1" t="s">
         <v>35</v>
       </c>
-      <c r="B73" s="0" t="n">
+      <c r="B73" s="1" t="n">
         <v>19000000</v>
       </c>
     </row>
     <row r="74" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A74" s="0" t="s">
+      <c r="A74" s="1" t="s">
         <v>27</v>
       </c>
-      <c r="B74" s="0" t="n">
+      <c r="B74" s="1" t="n">
         <v>10000000</v>
       </c>
     </row>
     <row r="75" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A75" s="0" t="s">
+      <c r="A75" s="1" t="s">
         <v>115</v>
       </c>
-      <c r="B75" s="0" t="n">
+      <c r="B75" s="1" t="n">
         <v>3435000000</v>
       </c>
     </row>
     <row r="76" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A76" s="0" t="s">
+      <c r="A76" s="1" t="s">
         <v>116</v>
       </c>
-      <c r="B76" s="0" t="n">
+      <c r="B76" s="1" t="n">
         <v>246000000</v>
       </c>
     </row>
     <row r="77" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A77" s="0" t="s">
+      <c r="A77" s="1" t="s">
         <v>117</v>
       </c>
-      <c r="B77" s="0" t="n">
+      <c r="B77" s="1" t="n">
         <v>82000000</v>
       </c>
     </row>
     <row r="78" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A78" s="0" t="s">
+      <c r="A78" s="1" t="s">
         <v>11</v>
       </c>
-      <c r="B78" s="0" t="n">
+      <c r="B78" s="1" t="n">
         <v>14767000000</v>
       </c>
     </row>
     <row r="79" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A79" s="0" t="s">
+      <c r="A79" s="1" t="s">
         <v>12</v>
       </c>
-      <c r="B79" s="0" t="n">
+      <c r="B79" s="1" t="n">
         <v>38891000000</v>
       </c>
     </row>
     <row r="80" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A80" s="3" t="s">
+      <c r="A80" s="1" t="s">
         <v>68</v>
       </c>
-      <c r="B80" s="3" t="n">
+      <c r="B80" s="1" t="n">
         <v>31000000</v>
       </c>
     </row>
     <row r="81" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A81" s="0" t="s">
+      <c r="A81" s="1" t="s">
         <v>118</v>
       </c>
-      <c r="B81" s="0" t="n">
+      <c r="B81" s="1" t="n">
         <v>11000000</v>
       </c>
     </row>
     <row r="82" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A82" s="0" t="s">
+      <c r="A82" s="1" t="s">
         <v>59</v>
       </c>
-      <c r="B82" s="0" t="n">
+      <c r="B82" s="1" t="n">
         <v>1000000</v>
       </c>
     </row>
     <row r="83" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A83" s="0" t="s">
+      <c r="A83" s="1" t="s">
         <v>29</v>
       </c>
-      <c r="B83" s="0" t="n">
+      <c r="B83" s="1" t="n">
         <v>2000000</v>
       </c>
     </row>
     <row r="84" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A84" s="0" t="s">
+      <c r="A84" s="1" t="s">
         <v>119</v>
       </c>
-      <c r="B84" s="0" t="n">
+      <c r="B84" s="1" t="n">
         <v>517000000</v>
       </c>
     </row>
     <row r="85" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A85" s="0" t="s">
+      <c r="A85" s="1" t="s">
         <v>60</v>
       </c>
-      <c r="B85" s="0" t="n">
+      <c r="B85" s="1" t="n">
         <v>20000000</v>
       </c>
     </row>
     <row r="86" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A86" s="0" t="s">
+      <c r="A86" s="1" t="s">
         <v>42</v>
       </c>
-      <c r="B86" s="0" t="n">
+      <c r="B86" s="1" t="n">
         <v>177000000</v>
       </c>
     </row>
     <row r="87" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A87" s="0" t="s">
+      <c r="A87" s="1" t="s">
         <v>120</v>
       </c>
-      <c r="B87" s="0" t="n">
+      <c r="B87" s="1" t="n">
         <v>13000000</v>
       </c>
     </row>
     <row r="88" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A88" s="0" t="s">
+      <c r="A88" s="1" t="s">
         <v>121</v>
       </c>
-      <c r="B88" s="0" t="n">
+      <c r="B88" s="1" t="n">
         <v>340000000</v>
       </c>
     </row>
     <row r="89" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A89" s="0" t="s">
+      <c r="A89" s="1" t="s">
         <v>122</v>
       </c>
-      <c r="B89" s="0" t="n">
+      <c r="B89" s="1" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="90" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A90" s="0" t="s">
+      <c r="A90" s="1" t="s">
         <v>22</v>
       </c>
-      <c r="B90" s="0" t="n">
+      <c r="B90" s="1" t="n">
         <v>2000000</v>
       </c>
     </row>
     <row r="91" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A91" s="0" t="s">
+      <c r="A91" s="1" t="s">
         <v>123</v>
       </c>
-      <c r="B91" s="0" t="n">
+      <c r="B91" s="1" t="n">
         <v>21000000</v>
       </c>
     </row>
     <row r="92" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A92" s="0" t="s">
+      <c r="A92" s="1" t="s">
         <v>124</v>
       </c>
-      <c r="B92" s="0" t="n">
+      <c r="B92" s="1" t="n">
         <v>25000000</v>
       </c>
     </row>
     <row r="93" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A93" s="0" t="s">
+      <c r="A93" s="1" t="s">
         <v>125</v>
       </c>
-      <c r="B93" s="0" t="n">
+      <c r="B93" s="1" t="n">
         <v>33000000</v>
       </c>
     </row>
     <row r="94" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A94" s="0" t="s">
+      <c r="A94" s="1" t="s">
         <v>70</v>
       </c>
-      <c r="B94" s="0" t="n">
+      <c r="B94" s="1" t="n">
         <v>58000000</v>
       </c>
     </row>
     <row r="95" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A95" s="0" t="s">
+      <c r="A95" s="1" t="s">
         <v>23</v>
       </c>
-      <c r="B95" s="0" t="n">
+      <c r="B95" s="1" t="n">
         <v>50000000</v>
       </c>
     </row>
     <row r="96" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A96" s="0" t="s">
+      <c r="A96" s="1" t="s">
         <v>126</v>
       </c>
-      <c r="B96" s="0" t="n">
+      <c r="B96" s="1" t="n">
         <v>82000000</v>
       </c>
     </row>
     <row r="97" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A97" s="0" t="s">
+      <c r="A97" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="B97" s="0" t="n">
+      <c r="B97" s="1" t="n">
         <v>8561000000</v>
       </c>
     </row>
     <row r="98" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A98" s="0" t="s">
+      <c r="A98" s="1" t="s">
         <v>127</v>
       </c>
-      <c r="B98" s="0" t="n">
+      <c r="B98" s="1" t="n">
         <v>340000000</v>
       </c>
     </row>
     <row r="99" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A99" s="0" t="s">
+      <c r="A99" s="1" t="s">
         <v>53</v>
       </c>
-      <c r="B99" s="0" t="n">
+      <c r="B99" s="1" t="n">
         <v>54000000</v>
       </c>
     </row>
     <row r="100" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A100" s="0" t="s">
+      <c r="A100" s="1" t="s">
         <v>128</v>
       </c>
-      <c r="B100" s="0" t="n">
+      <c r="B100" s="1" t="n">
         <v>15374000000</v>
       </c>
     </row>
     <row r="101" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A101" s="0" t="s">
+      <c r="A101" s="1" t="s">
         <v>129</v>
       </c>
-      <c r="B101" s="0" t="n">
+      <c r="B101" s="1" t="n">
         <v>237000000</v>
       </c>
     </row>
     <row r="102" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A102" s="0" t="s">
+      <c r="A102" s="1" t="s">
         <v>44</v>
       </c>
-      <c r="B102" s="0" t="n">
+      <c r="B102" s="1" t="n">
         <v>81000000</v>
       </c>
     </row>
     <row r="103" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A103" s="0" t="s">
+      <c r="A103" s="1" t="s">
         <v>130</v>
       </c>
-      <c r="B103" s="0" t="n">
+      <c r="B103" s="1" t="n">
         <v>47385000000</v>
       </c>
     </row>
     <row r="104" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A104" s="0" t="s">
+      <c r="A104" s="1" t="s">
         <v>13</v>
       </c>
-      <c r="B104" s="0" t="n">
+      <c r="B104" s="1" t="n">
         <v>599000000</v>
       </c>
     </row>
     <row r="105" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A105" s="0" t="s">
+      <c r="A105" s="1" t="s">
         <v>131</v>
       </c>
-      <c r="B105" s="0" t="n">
+      <c r="B105" s="1" t="n">
         <v>408000000</v>
       </c>
     </row>
@@ -4219,10 +4231,10 @@
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
   <dimension ref="A1:B105"/>
-  <sheetFormatPr defaultColWidth="8.5390625" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <sheetFormatPr defaultColWidth="8.54296875" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="32"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="0" width="20"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="32"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="1" width="20"/>
   </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -4234,826 +4246,826 @@
       </c>
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A2" s="0" t="s">
+      <c r="A2" s="1" t="s">
         <v>74</v>
       </c>
-      <c r="B2" s="0" t="n">
+      <c r="B2" s="1" t="n">
         <v>40000000000</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A3" s="0" t="s">
+      <c r="A3" s="1" t="s">
         <v>75</v>
       </c>
-      <c r="B3" s="0" t="n">
+      <c r="B3" s="1" t="n">
         <v>4800000000</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A4" s="0" t="s">
+      <c r="A4" s="1" t="s">
         <v>64</v>
       </c>
-      <c r="B4" s="0" t="n">
+      <c r="B4" s="1" t="n">
         <v>1823200000000</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A5" s="0" t="s">
+      <c r="A5" s="1" t="s">
         <v>76</v>
       </c>
-      <c r="B5" s="0" t="n">
+      <c r="B5" s="1" t="n">
         <v>240800000000</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A6" s="0" t="s">
+      <c r="A6" s="1" t="s">
         <v>54</v>
       </c>
-      <c r="B6" s="0" t="n">
+      <c r="B6" s="1" t="n">
         <v>332800000000</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A7" s="0" t="s">
+      <c r="A7" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="B7" s="0" t="n">
+      <c r="B7" s="1" t="n">
         <v>1452000000000</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A8" s="0" t="s">
+      <c r="A8" s="1" t="s">
         <v>57</v>
       </c>
-      <c r="B8" s="0" t="n">
+      <c r="B8" s="1" t="n">
         <v>4000000000</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A9" s="0" t="s">
+      <c r="A9" s="1" t="s">
         <v>77</v>
       </c>
-      <c r="B9" s="0" t="n">
+      <c r="B9" s="1" t="n">
         <v>1533600000000</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A10" s="0" t="s">
+      <c r="A10" s="1" t="s">
         <v>78</v>
       </c>
-      <c r="B10" s="0" t="n">
+      <c r="B10" s="1" t="n">
         <v>54400000000</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A11" s="0" t="s">
+      <c r="A11" s="1" t="s">
         <v>79</v>
       </c>
-      <c r="B11" s="0" t="n">
+      <c r="B11" s="1" t="n">
         <v>56000000000</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A12" s="0" t="s">
+      <c r="A12" s="1" t="s">
         <v>80</v>
       </c>
-      <c r="B12" s="0" t="n">
+      <c r="B12" s="1" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A13" s="0" t="s">
+      <c r="A13" s="1" t="s">
         <v>81</v>
       </c>
-      <c r="B13" s="0" t="n">
+      <c r="B13" s="1" t="n">
         <v>2400000000</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A14" s="0" t="s">
+      <c r="A14" s="1" t="s">
         <v>83</v>
       </c>
-      <c r="B14" s="0" t="n">
+      <c r="B14" s="1" t="n">
         <v>800000000</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A15" s="0" t="s">
+      <c r="A15" s="1" t="s">
         <v>16</v>
       </c>
-      <c r="B15" s="0" t="n">
+      <c r="B15" s="1" t="n">
         <v>170400000000</v>
       </c>
     </row>
     <row r="16" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A16" s="0" t="s">
+      <c r="A16" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="B16" s="0" t="n">
+      <c r="B16" s="1" t="n">
         <v>325600000000</v>
       </c>
     </row>
     <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A17" s="0" t="s">
+      <c r="A17" s="1" t="s">
         <v>84</v>
       </c>
-      <c r="B17" s="0" t="n">
+      <c r="B17" s="1" t="n">
         <v>182400000000</v>
       </c>
     </row>
     <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A18" s="0" t="s">
+      <c r="A18" s="1" t="s">
         <v>85</v>
       </c>
-      <c r="B18" s="0" t="n">
+      <c r="B18" s="1" t="n">
         <v>4800000000</v>
       </c>
     </row>
     <row r="19" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A19" s="0" t="s">
+      <c r="A19" s="1" t="s">
         <v>86</v>
       </c>
-      <c r="B19" s="0" t="n">
+      <c r="B19" s="1" t="n">
         <v>108000000000</v>
       </c>
     </row>
     <row r="20" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A20" s="0" t="s">
+      <c r="A20" s="1" t="s">
         <v>18</v>
       </c>
-      <c r="B20" s="0" t="n">
+      <c r="B20" s="1" t="n">
         <v>1971200000000</v>
       </c>
     </row>
     <row r="21" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A21" s="3" t="s">
+      <c r="A21" s="1" t="s">
         <v>36</v>
       </c>
-      <c r="B21" s="3" t="n">
+      <c r="B21" s="1" t="n">
         <v>78400000000</v>
       </c>
     </row>
     <row r="22" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A22" s="0" t="s">
+      <c r="A22" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="B22" s="0" t="n">
+      <c r="B22" s="1" t="n">
         <v>5071200000000</v>
       </c>
     </row>
     <row r="23" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A23" s="0" t="s">
+      <c r="A23" s="1" t="s">
         <v>39</v>
       </c>
-      <c r="B23" s="0" t="n">
+      <c r="B23" s="1" t="n">
         <v>72000000000</v>
       </c>
     </row>
     <row r="24" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A24" s="0" t="s">
+      <c r="A24" s="1" t="s">
         <v>88</v>
       </c>
-      <c r="B24" s="0" t="n">
+      <c r="B24" s="1" t="n">
         <v>20000000000</v>
       </c>
     </row>
     <row r="25" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A25" s="0" t="s">
+      <c r="A25" s="1" t="s">
         <v>31</v>
       </c>
-      <c r="B25" s="0" t="n">
+      <c r="B25" s="1" t="n">
         <v>56800000000</v>
       </c>
     </row>
     <row r="26" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A26" s="0" t="s">
+      <c r="A26" s="1" t="s">
         <v>89</v>
       </c>
-      <c r="B26" s="0" t="n">
+      <c r="B26" s="1" t="n">
         <v>3200000000</v>
       </c>
     </row>
     <row r="27" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A27" s="0" t="s">
+      <c r="A27" s="1" t="s">
         <v>30</v>
       </c>
-      <c r="B27" s="0" t="n">
+      <c r="B27" s="1" t="n">
         <v>800000000</v>
       </c>
     </row>
     <row r="28" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A28" s="0" t="s">
+      <c r="A28" s="1" t="s">
         <v>90</v>
       </c>
-      <c r="B28" s="0" t="n">
+      <c r="B28" s="1" t="n">
         <v>22400000000</v>
       </c>
     </row>
     <row r="29" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A29" s="0" t="s">
+      <c r="A29" s="1" t="s">
         <v>91</v>
       </c>
-      <c r="B29" s="0" t="n">
+      <c r="B29" s="1" t="n">
         <v>8800000000</v>
       </c>
     </row>
     <row r="30" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A30" s="0" t="s">
+      <c r="A30" s="1" t="s">
         <v>65</v>
       </c>
-      <c r="B30" s="0" t="n">
+      <c r="B30" s="1" t="n">
         <v>1427200000000</v>
       </c>
     </row>
     <row r="31" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A31" s="0" t="s">
+      <c r="A31" s="1" t="s">
         <v>92</v>
       </c>
-      <c r="B31" s="0" t="n">
+      <c r="B31" s="1" t="n">
         <v>31200000000</v>
       </c>
     </row>
     <row r="32" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A32" s="0" t="s">
+      <c r="A32" s="1" t="s">
         <v>132</v>
       </c>
-      <c r="B32" s="0" t="n">
+      <c r="B32" s="1" t="n">
         <v>20000000000</v>
       </c>
     </row>
     <row r="33" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A33" s="0" t="s">
+      <c r="A33" s="1" t="s">
         <v>94</v>
       </c>
-      <c r="B33" s="0" t="n">
+      <c r="B33" s="1" t="n">
         <v>6400000000</v>
       </c>
     </row>
     <row r="34" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A34" s="0" t="s">
+      <c r="A34" s="1" t="s">
         <v>61</v>
       </c>
-      <c r="B34" s="0" t="n">
+      <c r="B34" s="1" t="n">
         <v>20800000000</v>
       </c>
     </row>
     <row r="35" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A35" s="0" t="s">
+      <c r="A35" s="1" t="s">
         <v>95</v>
       </c>
-      <c r="B35" s="0" t="n">
+      <c r="B35" s="1" t="n">
         <v>6400000000</v>
       </c>
     </row>
     <row r="36" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A36" s="0" t="s">
+      <c r="A36" s="1" t="s">
         <v>96</v>
       </c>
-      <c r="B36" s="0" t="n">
+      <c r="B36" s="1" t="n">
         <v>16000000000</v>
       </c>
     </row>
     <row r="37" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A37" s="0" t="s">
+      <c r="A37" s="1" t="s">
         <v>40</v>
       </c>
-      <c r="B37" s="0" t="n">
+      <c r="B37" s="1" t="n">
         <v>18400000000</v>
       </c>
     </row>
     <row r="38" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A38" s="0" t="s">
+      <c r="A38" s="1" t="s">
         <v>58</v>
       </c>
-      <c r="B38" s="0" t="n">
+      <c r="B38" s="1" t="n">
         <v>800000000</v>
       </c>
     </row>
     <row r="39" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A39" s="0" t="s">
+      <c r="A39" s="1" t="s">
         <v>99</v>
       </c>
-      <c r="B39" s="0" t="n">
+      <c r="B39" s="1" t="n">
         <v>3200000000</v>
       </c>
     </row>
     <row r="40" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A40" s="0" t="s">
+      <c r="A40" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="B40" s="0" t="n">
+      <c r="B40" s="1" t="n">
         <v>520000000000</v>
       </c>
     </row>
     <row r="41" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A41" s="0" t="s">
+      <c r="A41" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="B41" s="0" t="n">
+      <c r="B41" s="1" t="n">
         <v>823200000000</v>
       </c>
     </row>
     <row r="42" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A42" s="0" t="s">
+      <c r="A42" s="1" t="s">
         <v>50</v>
       </c>
-      <c r="B42" s="0" t="n">
+      <c r="B42" s="1" t="n">
         <v>27190400000000</v>
       </c>
     </row>
     <row r="43" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A43" s="0" t="s">
+      <c r="A43" s="1" t="s">
         <v>100</v>
       </c>
-      <c r="B43" s="0" t="n">
+      <c r="B43" s="1" t="n">
         <v>2971200000000</v>
       </c>
     </row>
     <row r="44" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A44" s="0" t="s">
+      <c r="A44" s="1" t="s">
         <v>133</v>
       </c>
-      <c r="B44" s="0" t="n">
+      <c r="B44" s="1" t="n">
         <v>8000000000</v>
       </c>
     </row>
     <row r="45" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A45" s="0" t="s">
+      <c r="A45" s="1" t="s">
         <v>66</v>
       </c>
-      <c r="B45" s="0" t="n">
+      <c r="B45" s="1" t="n">
         <v>736000000000</v>
       </c>
     </row>
     <row r="46" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A46" s="0" t="s">
+      <c r="A46" s="1" t="s">
         <v>101</v>
       </c>
-      <c r="B46" s="0" t="n">
+      <c r="B46" s="1" t="n">
         <v>32000000000</v>
       </c>
     </row>
     <row r="47" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A47" s="0" t="s">
+      <c r="A47" s="1" t="s">
         <v>102</v>
       </c>
-      <c r="B47" s="0" t="n">
+      <c r="B47" s="1" t="n">
         <v>22400000000</v>
       </c>
     </row>
     <row r="48" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A48" s="0" t="s">
+      <c r="A48" s="1" t="s">
         <v>103</v>
       </c>
-      <c r="B48" s="0" t="n">
+      <c r="B48" s="1" t="n">
         <v>16800000000</v>
       </c>
     </row>
     <row r="49" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A49" s="0" t="s">
+      <c r="A49" s="1" t="s">
         <v>67</v>
       </c>
-      <c r="B49" s="0" t="n">
+      <c r="B49" s="1" t="n">
         <v>3200000000</v>
       </c>
     </row>
     <row r="50" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A50" s="0" t="s">
+      <c r="A50" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="B50" s="0" t="n">
+      <c r="B50" s="1" t="n">
         <v>1464000000000</v>
       </c>
     </row>
     <row r="51" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A51" s="0" t="s">
+      <c r="A51" s="1" t="s">
         <v>104</v>
       </c>
-      <c r="B51" s="0" t="n">
+      <c r="B51" s="1" t="n">
         <v>1427200000000</v>
       </c>
     </row>
     <row r="52" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A52" s="0" t="s">
+      <c r="A52" s="1" t="s">
         <v>19</v>
       </c>
-      <c r="B52" s="0" t="n">
+      <c r="B52" s="1" t="n">
         <v>4800000000</v>
       </c>
     </row>
     <row r="53" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A53" s="0" t="s">
+      <c r="A53" s="1" t="s">
         <v>105</v>
       </c>
-      <c r="B53" s="0" t="n">
+      <c r="B53" s="1" t="n">
         <v>1204000000000</v>
       </c>
     </row>
     <row r="54" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A54" s="0" t="s">
+      <c r="A54" s="1" t="s">
         <v>107</v>
       </c>
-      <c r="B54" s="0" t="n">
+      <c r="B54" s="1" t="n">
         <v>1721600000000</v>
       </c>
     </row>
     <row r="55" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A55" s="0" t="s">
+      <c r="A55" s="1" t="s">
         <v>51</v>
       </c>
-      <c r="B55" s="0" t="n">
+      <c r="B55" s="1" t="n">
         <v>224000000000</v>
       </c>
     </row>
     <row r="56" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A56" s="0" t="s">
+      <c r="A56" s="1" t="s">
         <v>20</v>
       </c>
-      <c r="B56" s="0" t="n">
+      <c r="B56" s="1" t="n">
         <v>249600000000</v>
       </c>
     </row>
     <row r="57" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A57" s="0" t="s">
+      <c r="A57" s="1" t="s">
         <v>33</v>
       </c>
-      <c r="B57" s="0" t="n">
+      <c r="B57" s="1" t="n">
         <v>4800000000</v>
       </c>
     </row>
     <row r="58" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A58" s="0" t="s">
+      <c r="A58" s="1" t="s">
         <v>47</v>
       </c>
-      <c r="B58" s="0" t="n">
+      <c r="B58" s="1" t="n">
         <v>2265600000000</v>
       </c>
     </row>
     <row r="59" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A59" s="0" t="s">
+      <c r="A59" s="1" t="s">
         <v>109</v>
       </c>
-      <c r="B59" s="0" t="n">
+      <c r="B59" s="1" t="n">
         <v>509600000000</v>
       </c>
     </row>
     <row r="60" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A60" s="0" t="s">
+      <c r="A60" s="1" t="s">
         <v>134</v>
       </c>
-      <c r="B60" s="0" t="n">
+      <c r="B60" s="1" t="n">
         <v>49600000000</v>
       </c>
     </row>
     <row r="61" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A61" s="0" t="s">
+      <c r="A61" s="1" t="s">
         <v>110</v>
       </c>
-      <c r="B61" s="0" t="n">
+      <c r="B61" s="1" t="n">
         <v>74400000000</v>
       </c>
     </row>
     <row r="62" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A62" s="0" t="s">
+      <c r="A62" s="1" t="s">
         <v>111</v>
       </c>
-      <c r="B62" s="0" t="n">
+      <c r="B62" s="1" t="n">
         <v>29600000000</v>
       </c>
     </row>
     <row r="63" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A63" s="0" t="s">
+      <c r="A63" s="1" t="s">
         <v>113</v>
       </c>
-      <c r="B63" s="0" t="n">
+      <c r="B63" s="1" t="n">
         <v>4730400000000</v>
       </c>
     </row>
     <row r="64" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A64" s="0" t="s">
+      <c r="A64" s="1" t="s">
         <v>48</v>
       </c>
-      <c r="B64" s="0" t="n">
+      <c r="B64" s="1" t="n">
         <v>1175200000000</v>
       </c>
     </row>
     <row r="65" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A65" s="0" t="s">
+      <c r="A65" s="1" t="s">
         <v>114</v>
       </c>
-      <c r="B65" s="0" t="n">
+      <c r="B65" s="1" t="n">
         <v>520800000000</v>
       </c>
     </row>
     <row r="66" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A66" s="0" t="s">
+      <c r="A66" s="1" t="s">
         <v>21</v>
       </c>
-      <c r="B66" s="0" t="n">
+      <c r="B66" s="1" t="n">
         <v>473600000000</v>
       </c>
     </row>
     <row r="67" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A67" s="0" t="s">
+      <c r="A67" s="1" t="s">
         <v>34</v>
       </c>
-      <c r="B67" s="0" t="n">
+      <c r="B67" s="1" t="n">
         <v>136000000000</v>
       </c>
     </row>
     <row r="68" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A68" s="0" t="s">
+      <c r="A68" s="1" t="s">
         <v>26</v>
       </c>
-      <c r="B68" s="0" t="n">
+      <c r="B68" s="1" t="n">
         <v>240000000000</v>
       </c>
     </row>
     <row r="69" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A69" s="0" t="s">
+      <c r="A69" s="1" t="s">
         <v>35</v>
       </c>
-      <c r="B69" s="0" t="n">
+      <c r="B69" s="1" t="n">
         <v>79200000000</v>
       </c>
     </row>
     <row r="70" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A70" s="0" t="s">
+      <c r="A70" s="1" t="s">
         <v>27</v>
       </c>
-      <c r="B70" s="0" t="n">
+      <c r="B70" s="1" t="n">
         <v>74400000000</v>
       </c>
     </row>
     <row r="71" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A71" s="0" t="s">
+      <c r="A71" s="1" t="s">
         <v>115</v>
       </c>
-      <c r="B71" s="0" t="n">
+      <c r="B71" s="1" t="n">
         <v>19064800000000</v>
       </c>
     </row>
     <row r="72" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A72" s="0" t="s">
+      <c r="A72" s="1" t="s">
         <v>116</v>
       </c>
-      <c r="B72" s="0" t="n">
+      <c r="B72" s="1" t="n">
         <v>227200000000</v>
       </c>
     </row>
     <row r="73" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A73" s="0" t="s">
+      <c r="A73" s="1" t="s">
         <v>117</v>
       </c>
-      <c r="B73" s="0" t="n">
+      <c r="B73" s="1" t="n">
         <v>84000000000</v>
       </c>
     </row>
     <row r="74" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A74" s="0" t="s">
+      <c r="A74" s="1" t="s">
         <v>11</v>
       </c>
-      <c r="B74" s="0" t="n">
+      <c r="B74" s="1" t="n">
         <v>38207200000000</v>
       </c>
     </row>
     <row r="75" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A75" s="0" t="s">
+      <c r="A75" s="1" t="s">
         <v>135</v>
       </c>
-      <c r="B75" s="0" t="n">
+      <c r="B75" s="1" t="n">
         <v>45600000000</v>
       </c>
     </row>
     <row r="76" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A76" s="0" t="s">
+      <c r="A76" s="1" t="s">
         <v>12</v>
       </c>
-      <c r="B76" s="0" t="n">
+      <c r="B76" s="1" t="n">
         <v>7454400000000</v>
       </c>
     </row>
     <row r="77" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A77" s="3" t="s">
+      <c r="A77" s="1" t="s">
         <v>68</v>
       </c>
-      <c r="B77" s="3" t="n">
+      <c r="B77" s="1" t="n">
         <v>169600000000</v>
       </c>
     </row>
     <row r="78" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A78" s="3" t="s">
+      <c r="A78" s="1" t="s">
         <v>118</v>
       </c>
-      <c r="B78" s="3" t="n">
+      <c r="B78" s="1" t="n">
         <v>38400000000</v>
       </c>
     </row>
     <row r="79" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A79" s="3" t="s">
+      <c r="A79" s="1" t="s">
         <v>59</v>
       </c>
-      <c r="B79" s="3" t="n">
+      <c r="B79" s="1" t="n">
         <v>11200000000</v>
       </c>
     </row>
     <row r="80" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A80" s="3" t="s">
+      <c r="A80" s="1" t="s">
         <v>136</v>
       </c>
-      <c r="B80" s="3" t="n">
+      <c r="B80" s="1" t="n">
         <v>800000000</v>
       </c>
     </row>
     <row r="81" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A81" s="3" t="s">
+      <c r="A81" s="1" t="s">
         <v>137</v>
       </c>
-      <c r="B81" s="3" t="n">
+      <c r="B81" s="1" t="n">
         <v>4800000000</v>
       </c>
     </row>
     <row r="82" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A82" s="3" t="s">
+      <c r="A82" s="1" t="s">
         <v>29</v>
       </c>
-      <c r="B82" s="3" t="n">
+      <c r="B82" s="1" t="n">
         <v>8000000000</v>
       </c>
     </row>
     <row r="83" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A83" s="3" t="s">
+      <c r="A83" s="1" t="s">
         <v>46</v>
       </c>
-      <c r="B83" s="3" t="n">
+      <c r="B83" s="1" t="n">
         <v>5600000000</v>
       </c>
     </row>
     <row r="84" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A84" s="3" t="s">
+      <c r="A84" s="1" t="s">
         <v>60</v>
       </c>
-      <c r="B84" s="3" t="n">
+      <c r="B84" s="1" t="n">
         <v>2400000000</v>
       </c>
     </row>
     <row r="85" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A85" s="3" t="s">
+      <c r="A85" s="1" t="s">
         <v>42</v>
       </c>
-      <c r="B85" s="3" t="n">
+      <c r="B85" s="1" t="n">
         <v>68000000000</v>
       </c>
     </row>
     <row r="86" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A86" s="3" t="s">
+      <c r="A86" s="1" t="s">
         <v>121</v>
       </c>
-      <c r="B86" s="3" t="n">
+      <c r="B86" s="1" t="n">
         <v>192800000000</v>
       </c>
     </row>
     <row r="87" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A87" s="0" t="s">
+      <c r="A87" s="1" t="s">
         <v>122</v>
       </c>
-      <c r="B87" s="0" t="n">
+      <c r="B87" s="1" t="n">
         <v>4800000000</v>
       </c>
     </row>
     <row r="88" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A88" s="0" t="s">
+      <c r="A88" s="1" t="s">
         <v>22</v>
       </c>
-      <c r="B88" s="0" t="n">
+      <c r="B88" s="1" t="n">
         <v>4800000000</v>
       </c>
     </row>
     <row r="89" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A89" s="0" t="s">
+      <c r="A89" s="1" t="s">
         <v>43</v>
       </c>
-      <c r="B89" s="0" t="n">
+      <c r="B89" s="1" t="n">
         <v>5600000000</v>
       </c>
     </row>
     <row r="90" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A90" s="0" t="s">
+      <c r="A90" s="1" t="s">
         <v>123</v>
       </c>
-      <c r="B90" s="0" t="n">
+      <c r="B90" s="1" t="n">
         <v>78400000000</v>
       </c>
     </row>
     <row r="91" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A91" s="0" t="s">
+      <c r="A91" s="1" t="s">
         <v>124</v>
       </c>
-      <c r="B91" s="0" t="n">
+      <c r="B91" s="1" t="n">
         <v>70400000000</v>
       </c>
     </row>
     <row r="92" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A92" s="0" t="s">
+      <c r="A92" s="1" t="s">
         <v>125</v>
       </c>
-      <c r="B92" s="0" t="n">
+      <c r="B92" s="1" t="n">
         <v>242400000000</v>
       </c>
     </row>
     <row r="93" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A93" s="0" t="s">
+      <c r="A93" s="1" t="s">
         <v>70</v>
       </c>
-      <c r="B93" s="0" t="n">
+      <c r="B93" s="1" t="n">
         <v>52000000000</v>
       </c>
     </row>
     <row r="94" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A94" s="0" t="s">
+      <c r="A94" s="1" t="s">
         <v>23</v>
       </c>
-      <c r="B94" s="0" t="n">
+      <c r="B94" s="1" t="n">
         <v>2400000000</v>
       </c>
     </row>
     <row r="95" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A95" s="0" t="s">
+      <c r="A95" s="1" t="s">
         <v>126</v>
       </c>
-      <c r="B95" s="0" t="n">
+      <c r="B95" s="1" t="n">
         <v>11160000000000</v>
       </c>
     </row>
     <row r="96" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A96" s="0" t="s">
+      <c r="A96" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="B96" s="0" t="n">
+      <c r="B96" s="1" t="n">
         <v>13115200000000</v>
       </c>
     </row>
     <row r="97" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A97" s="0" t="s">
+      <c r="A97" s="1" t="s">
         <v>127</v>
       </c>
-      <c r="B97" s="0" t="n">
+      <c r="B97" s="1" t="n">
         <v>11200000000</v>
       </c>
     </row>
     <row r="98" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A98" s="3" t="s">
+      <c r="A98" s="1" t="s">
         <v>53</v>
       </c>
-      <c r="B98" s="3" t="n">
+      <c r="B98" s="1" t="n">
         <v>883200000000</v>
       </c>
     </row>
     <row r="99" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A99" s="3" t="s">
+      <c r="A99" s="1" t="s">
         <v>128</v>
       </c>
-      <c r="B99" s="3" t="n">
+      <c r="B99" s="1" t="n">
         <v>6560800000000</v>
       </c>
     </row>
     <row r="100" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A100" s="0" t="s">
+      <c r="A100" s="1" t="s">
         <v>129</v>
       </c>
-      <c r="B100" s="0" t="n">
+      <c r="B100" s="1" t="n">
         <v>116800000000</v>
       </c>
     </row>
     <row r="101" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A101" s="0" t="s">
+      <c r="A101" s="1" t="s">
         <v>44</v>
       </c>
-      <c r="B101" s="0" t="n">
+      <c r="B101" s="1" t="n">
         <v>1476800000000</v>
       </c>
     </row>
     <row r="102" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A102" s="0" t="s">
+      <c r="A102" s="1" t="s">
         <v>130</v>
       </c>
-      <c r="B102" s="0" t="n">
+      <c r="B102" s="1" t="n">
         <v>4433600000000</v>
       </c>
     </row>
     <row r="103" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A103" s="0" t="s">
+      <c r="A103" s="1" t="s">
         <v>13</v>
       </c>
-      <c r="B103" s="0" t="n">
+      <c r="B103" s="1" t="n">
         <v>488000000000</v>
       </c>
     </row>
     <row r="104" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A104" s="0" t="s">
+      <c r="A104" s="1" t="s">
         <v>131</v>
       </c>
-      <c r="B104" s="0" t="n">
+      <c r="B104" s="1" t="n">
         <v>212800000000</v>
       </c>
     </row>
@@ -5082,10 +5094,10 @@
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
   <dimension ref="A1:B71"/>
-  <sheetFormatPr defaultColWidth="8.5390625" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <sheetFormatPr defaultColWidth="8.54296875" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="32"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="0" width="20"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="32"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="1" width="20"/>
   </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -5097,554 +5109,554 @@
       </c>
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A2" s="0" t="s">
+      <c r="A2" s="1" t="s">
         <v>74</v>
       </c>
-      <c r="B2" s="0" t="n">
+      <c r="B2" s="1" t="n">
         <v>66000000</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A3" s="0" t="s">
+      <c r="A3" s="1" t="s">
         <v>64</v>
       </c>
-      <c r="B3" s="0" t="n">
+      <c r="B3" s="1" t="n">
         <v>59000000</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A4" s="0" t="s">
+      <c r="A4" s="1" t="s">
         <v>54</v>
       </c>
-      <c r="B4" s="0" t="n">
+      <c r="B4" s="1" t="n">
         <v>500000000</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A5" s="0" t="s">
+      <c r="A5" s="1" t="s">
         <v>62</v>
       </c>
-      <c r="B5" s="0" t="n">
+      <c r="B5" s="1" t="n">
         <v>163000000</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A6" s="0" t="s">
+      <c r="A6" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="B6" s="0" t="n">
+      <c r="B6" s="1" t="n">
         <v>75433000000</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A7" s="0" t="s">
+      <c r="A7" s="1" t="s">
         <v>79</v>
       </c>
-      <c r="B7" s="0" t="n">
+      <c r="B7" s="1" t="n">
         <v>293000000</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A8" s="0" t="s">
+      <c r="A8" s="1" t="s">
         <v>16</v>
       </c>
-      <c r="B8" s="0" t="n">
+      <c r="B8" s="1" t="n">
         <v>1000000</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A9" s="0" t="s">
+      <c r="A9" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="B9" s="0" t="n">
+      <c r="B9" s="1" t="n">
         <v>1547000000</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A10" s="0" t="s">
+      <c r="A10" s="1" t="s">
         <v>85</v>
       </c>
-      <c r="B10" s="0" t="n">
+      <c r="B10" s="1" t="n">
         <v>192000000</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A11" s="0" t="s">
+      <c r="A11" s="1" t="s">
         <v>18</v>
       </c>
-      <c r="B11" s="0" t="n">
+      <c r="B11" s="1" t="n">
         <v>4346000000</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A12" s="0" t="s">
+      <c r="A12" s="1" t="s">
         <v>36</v>
       </c>
-      <c r="B12" s="0" t="n">
+      <c r="B12" s="1" t="n">
         <v>1181000000</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A13" s="0" t="s">
+      <c r="A13" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="B13" s="0" t="n">
+      <c r="B13" s="1" t="n">
         <v>146347000000</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A14" s="0" t="s">
+      <c r="A14" s="1" t="s">
         <v>39</v>
       </c>
-      <c r="B14" s="0" t="n">
+      <c r="B14" s="1" t="n">
         <v>4554000000</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A15" s="0" t="s">
+      <c r="A15" s="1" t="s">
         <v>89</v>
       </c>
-      <c r="B15" s="0" t="n">
+      <c r="B15" s="1" t="n">
         <v>1050000000</v>
       </c>
     </row>
     <row r="16" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A16" s="0" t="s">
+      <c r="A16" s="1" t="s">
         <v>30</v>
       </c>
-      <c r="B16" s="0" t="n">
+      <c r="B16" s="1" t="n">
         <v>88000000</v>
       </c>
     </row>
     <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A17" s="0" t="s">
+      <c r="A17" s="1" t="s">
         <v>65</v>
       </c>
-      <c r="B17" s="0" t="n">
+      <c r="B17" s="1" t="n">
         <v>16000000</v>
       </c>
     </row>
     <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A18" s="0" t="s">
+      <c r="A18" s="1" t="s">
         <v>138</v>
       </c>
-      <c r="B18" s="0" t="n">
+      <c r="B18" s="1" t="n">
         <v>144000000</v>
       </c>
     </row>
     <row r="19" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A19" s="0" t="s">
+      <c r="A19" s="1" t="s">
         <v>95</v>
       </c>
-      <c r="B19" s="0" t="n">
+      <c r="B19" s="1" t="n">
         <v>201000000</v>
       </c>
     </row>
     <row r="20" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A20" s="0" t="s">
+      <c r="A20" s="1" t="s">
         <v>71</v>
       </c>
-      <c r="B20" s="0" t="n">
+      <c r="B20" s="1" t="n">
         <v>183000000</v>
       </c>
     </row>
     <row r="21" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A21" s="0" t="s">
+      <c r="A21" s="1" t="s">
         <v>99</v>
       </c>
-      <c r="B21" s="0" t="n">
+      <c r="B21" s="1" t="n">
         <v>276000000</v>
       </c>
     </row>
     <row r="22" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A22" s="0" t="s">
+      <c r="A22" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="B22" s="0" t="n">
+      <c r="B22" s="1" t="n">
         <v>122253000000</v>
       </c>
     </row>
     <row r="23" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A23" s="0" t="s">
+      <c r="A23" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="B23" s="0" t="n">
+      <c r="B23" s="1" t="n">
         <v>21734000000</v>
       </c>
     </row>
     <row r="24" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A24" s="0" t="s">
+      <c r="A24" s="1" t="s">
         <v>50</v>
       </c>
-      <c r="B24" s="0" t="n">
+      <c r="B24" s="1" t="n">
         <v>1203000000</v>
       </c>
     </row>
     <row r="25" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A25" s="0" t="s">
+      <c r="A25" s="1" t="s">
         <v>133</v>
       </c>
-      <c r="B25" s="0" t="n">
+      <c r="B25" s="1" t="n">
         <v>14000000</v>
       </c>
     </row>
     <row r="26" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A26" s="0" t="s">
+      <c r="A26" s="1" t="s">
         <v>101</v>
       </c>
-      <c r="B26" s="0" t="n">
+      <c r="B26" s="1" t="n">
         <v>10000000</v>
       </c>
     </row>
     <row r="27" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A27" s="0" t="s">
+      <c r="A27" s="1" t="s">
         <v>103</v>
       </c>
-      <c r="B27" s="0" t="n">
+      <c r="B27" s="1" t="n">
         <v>340000000</v>
       </c>
     </row>
     <row r="28" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A28" s="0" t="s">
+      <c r="A28" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="B28" s="0" t="n">
+      <c r="B28" s="1" t="n">
         <v>25605000000</v>
       </c>
     </row>
     <row r="29" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A29" s="0" t="s">
+      <c r="A29" s="1" t="s">
         <v>19</v>
       </c>
-      <c r="B29" s="0" t="n">
+      <c r="B29" s="1" t="n">
         <v>971000000</v>
       </c>
     </row>
     <row r="30" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A30" s="0" t="s">
+      <c r="A30" s="1" t="s">
         <v>139</v>
       </c>
-      <c r="B30" s="0" t="n">
+      <c r="B30" s="1" t="n">
         <v>4000000</v>
       </c>
     </row>
     <row r="31" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A31" s="0" t="s">
+      <c r="A31" s="1" t="s">
         <v>140</v>
       </c>
-      <c r="B31" s="0" t="n">
+      <c r="B31" s="1" t="n">
         <v>2000000</v>
       </c>
     </row>
     <row r="32" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A32" s="0" t="s">
+      <c r="A32" s="1" t="s">
         <v>107</v>
       </c>
-      <c r="B32" s="0" t="n">
+      <c r="B32" s="1" t="n">
         <v>148000000</v>
       </c>
     </row>
     <row r="33" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A33" s="0" t="s">
+      <c r="A33" s="1" t="s">
         <v>20</v>
       </c>
-      <c r="B33" s="0" t="n">
+      <c r="B33" s="1" t="n">
         <v>1160000000</v>
       </c>
     </row>
     <row r="34" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A34" s="0" t="s">
+      <c r="A34" s="1" t="s">
         <v>108</v>
       </c>
-      <c r="B34" s="0" t="n">
+      <c r="B34" s="1" t="n">
         <v>1170000000</v>
       </c>
     </row>
     <row r="35" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A35" s="0" t="s">
+      <c r="A35" s="1" t="s">
         <v>141</v>
       </c>
-      <c r="B35" s="0" t="n">
+      <c r="B35" s="1" t="n">
         <v>142000000</v>
       </c>
     </row>
     <row r="36" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A36" s="0" t="s">
+      <c r="A36" s="1" t="s">
         <v>33</v>
       </c>
-      <c r="B36" s="0" t="n">
+      <c r="B36" s="1" t="n">
         <v>14000000</v>
       </c>
     </row>
     <row r="37" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A37" s="0" t="s">
+      <c r="A37" s="1" t="s">
         <v>47</v>
       </c>
-      <c r="B37" s="0" t="n">
+      <c r="B37" s="1" t="n">
         <v>1792000000</v>
       </c>
     </row>
     <row r="38" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A38" s="0" t="s">
+      <c r="A38" s="1" t="s">
         <v>109</v>
       </c>
-      <c r="B38" s="0" t="n">
+      <c r="B38" s="1" t="n">
         <v>3000000</v>
       </c>
     </row>
     <row r="39" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A39" s="0" t="s">
+      <c r="A39" s="1" t="s">
         <v>142</v>
       </c>
-      <c r="B39" s="0" t="n">
+      <c r="B39" s="1" t="n">
         <v>1000000</v>
       </c>
     </row>
     <row r="40" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A40" s="0" t="s">
+      <c r="A40" s="1" t="s">
         <v>110</v>
       </c>
-      <c r="B40" s="0" t="n">
+      <c r="B40" s="1" t="n">
         <v>497000000</v>
       </c>
     </row>
     <row r="41" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A41" s="0" t="s">
+      <c r="A41" s="1" t="s">
         <v>63</v>
       </c>
-      <c r="B41" s="0" t="n">
+      <c r="B41" s="1" t="n">
         <v>2000000</v>
       </c>
     </row>
     <row r="42" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A42" s="0" t="s">
+      <c r="A42" s="1" t="s">
         <v>111</v>
       </c>
-      <c r="B42" s="0" t="n">
+      <c r="B42" s="1" t="n">
         <v>825000000</v>
       </c>
     </row>
     <row r="43" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A43" s="0" t="s">
+      <c r="A43" s="1" t="s">
         <v>113</v>
       </c>
-      <c r="B43" s="0" t="n">
+      <c r="B43" s="1" t="n">
         <v>287000000</v>
       </c>
     </row>
     <row r="44" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A44" s="0" t="s">
+      <c r="A44" s="1" t="s">
         <v>45</v>
       </c>
-      <c r="B44" s="0" t="n">
+      <c r="B44" s="1" t="n">
         <v>600000000</v>
       </c>
     </row>
     <row r="45" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A45" s="0" t="s">
+      <c r="A45" s="1" t="s">
         <v>48</v>
       </c>
-      <c r="B45" s="0" t="n">
+      <c r="B45" s="1" t="n">
         <v>2000000</v>
       </c>
     </row>
     <row r="46" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A46" s="0" t="s">
+      <c r="A46" s="1" t="s">
         <v>21</v>
       </c>
-      <c r="B46" s="0" t="n">
+      <c r="B46" s="1" t="n">
         <v>207000000</v>
       </c>
     </row>
     <row r="47" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A47" s="0" t="s">
+      <c r="A47" s="1" t="s">
         <v>26</v>
       </c>
-      <c r="B47" s="0" t="n">
+      <c r="B47" s="1" t="n">
         <v>102000000</v>
       </c>
     </row>
     <row r="48" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A48" s="0" t="s">
+      <c r="A48" s="1" t="s">
         <v>35</v>
       </c>
-      <c r="B48" s="0" t="n">
+      <c r="B48" s="1" t="n">
         <v>262000000</v>
       </c>
     </row>
     <row r="49" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A49" s="0" t="s">
+      <c r="A49" s="1" t="s">
         <v>27</v>
       </c>
-      <c r="B49" s="0" t="n">
+      <c r="B49" s="1" t="n">
         <v>22687000000</v>
       </c>
     </row>
     <row r="50" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A50" s="0" t="s">
+      <c r="A50" s="1" t="s">
         <v>55</v>
       </c>
-      <c r="B50" s="0" t="n">
+      <c r="B50" s="1" t="n">
         <v>3000000</v>
       </c>
     </row>
     <row r="51" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A51" s="0" t="s">
+      <c r="A51" s="1" t="s">
         <v>117</v>
       </c>
-      <c r="B51" s="0" t="n">
+      <c r="B51" s="1" t="n">
         <v>11000000</v>
       </c>
     </row>
     <row r="52" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A52" s="0" t="s">
+      <c r="A52" s="1" t="s">
         <v>11</v>
       </c>
-      <c r="B52" s="0" t="n">
+      <c r="B52" s="1" t="n">
         <v>71719000000</v>
       </c>
     </row>
     <row r="53" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A53" s="0" t="s">
+      <c r="A53" s="1" t="s">
         <v>118</v>
       </c>
-      <c r="B53" s="0" t="n">
+      <c r="B53" s="1" t="n">
         <v>402000000</v>
       </c>
     </row>
     <row r="54" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A54" s="0" t="s">
+      <c r="A54" s="1" t="s">
         <v>136</v>
       </c>
-      <c r="B54" s="0" t="n">
+      <c r="B54" s="1" t="n">
         <v>56000000</v>
       </c>
     </row>
     <row r="55" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A55" s="0" t="s">
+      <c r="A55" s="1" t="s">
         <v>29</v>
       </c>
-      <c r="B55" s="0" t="n">
+      <c r="B55" s="1" t="n">
         <v>9893000000</v>
       </c>
     </row>
     <row r="56" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A56" s="0" t="s">
+      <c r="A56" s="1" t="s">
         <v>46</v>
       </c>
-      <c r="B56" s="0" t="n">
+      <c r="B56" s="1" t="n">
         <v>326000000</v>
       </c>
     </row>
     <row r="57" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A57" s="0" t="s">
+      <c r="A57" s="1" t="s">
         <v>60</v>
       </c>
-      <c r="B57" s="0" t="n">
+      <c r="B57" s="1" t="n">
         <v>868000000</v>
       </c>
     </row>
     <row r="58" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A58" s="0" t="s">
+      <c r="A58" s="1" t="s">
         <v>52</v>
       </c>
-      <c r="B58" s="0" t="n">
+      <c r="B58" s="1" t="n">
         <v>1000000</v>
       </c>
     </row>
     <row r="59" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A59" s="0" t="s">
+      <c r="A59" s="1" t="s">
         <v>122</v>
       </c>
-      <c r="B59" s="0" t="n">
+      <c r="B59" s="1" t="n">
         <v>1000000</v>
       </c>
     </row>
     <row r="60" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A60" s="0" t="s">
+      <c r="A60" s="1" t="s">
         <v>22</v>
       </c>
-      <c r="B60" s="0" t="n">
+      <c r="B60" s="1" t="n">
         <v>375000000</v>
       </c>
     </row>
     <row r="61" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A61" s="0" t="s">
+      <c r="A61" s="1" t="s">
         <v>43</v>
       </c>
-      <c r="B61" s="0" t="n">
+      <c r="B61" s="1" t="n">
         <v>269000000</v>
       </c>
     </row>
     <row r="62" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A62" s="0" t="s">
+      <c r="A62" s="1" t="s">
         <v>23</v>
       </c>
-      <c r="B62" s="0" t="n">
+      <c r="B62" s="1" t="n">
         <v>550000000</v>
       </c>
     </row>
     <row r="63" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A63" s="0" t="s">
+      <c r="A63" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="B63" s="0" t="n">
+      <c r="B63" s="1" t="n">
         <v>218016000000</v>
       </c>
     </row>
     <row r="64" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A64" s="0" t="s">
+      <c r="A64" s="1" t="s">
         <v>53</v>
       </c>
-      <c r="B64" s="0" t="n">
+      <c r="B64" s="1" t="n">
         <v>32039000000</v>
       </c>
     </row>
     <row r="65" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A65" s="0" t="s">
+      <c r="A65" s="1" t="s">
         <v>129</v>
       </c>
-      <c r="B65" s="0" t="n">
+      <c r="B65" s="1" t="n">
         <v>28000000</v>
       </c>
     </row>
     <row r="66" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A66" s="0" t="s">
+      <c r="A66" s="1" t="s">
         <v>44</v>
       </c>
-      <c r="B66" s="0" t="n">
+      <c r="B66" s="1" t="n">
         <v>1375000000</v>
       </c>
     </row>
     <row r="67" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A67" s="0" t="s">
+      <c r="A67" s="1" t="s">
         <v>130</v>
       </c>
-      <c r="B67" s="0" t="n">
+      <c r="B67" s="1" t="n">
         <v>731000000</v>
       </c>
     </row>
     <row r="68" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A68" s="0" t="s">
+      <c r="A68" s="1" t="s">
         <v>13</v>
       </c>
-      <c r="B68" s="0" t="n">
+      <c r="B68" s="1" t="n">
         <v>3116000000</v>
       </c>
     </row>
     <row r="69" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A69" s="0" t="s">
+      <c r="A69" s="1" t="s">
         <v>37</v>
       </c>
-      <c r="B69" s="0" t="n">
+      <c r="B69" s="1" t="n">
         <v>45000000</v>
       </c>
     </row>
     <row r="70" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A70" s="0" t="s">
+      <c r="A70" s="1" t="s">
         <v>56</v>
       </c>
-      <c r="B70" s="0" t="n">
+      <c r="B70" s="1" t="n">
         <v>502000000</v>
       </c>
     </row>
@@ -5673,10 +5685,10 @@
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
   <dimension ref="A1:B44"/>
-  <sheetFormatPr defaultColWidth="8.5390625" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <sheetFormatPr defaultColWidth="8.54296875" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="32"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="0" width="20"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="32"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="1" width="20"/>
   </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -5688,338 +5700,338 @@
       </c>
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A2" s="0" t="s">
+      <c r="A2" s="1" t="s">
         <v>75</v>
       </c>
-      <c r="B2" s="0" t="n">
+      <c r="B2" s="1" t="n">
         <v>522000000</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A3" s="0" t="s">
+      <c r="A3" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="B3" s="0" t="n">
+      <c r="B3" s="1" t="n">
         <v>74039000000</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A4" s="0" t="s">
+      <c r="A4" s="1" t="s">
         <v>143</v>
       </c>
-      <c r="B4" s="0" t="n">
+      <c r="B4" s="1" t="n">
         <v>2264000000</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A5" s="0" t="s">
+      <c r="A5" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="B5" s="0" t="n">
+      <c r="B5" s="1" t="n">
         <v>5049000000</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A6" s="0" t="s">
+      <c r="A6" s="1" t="s">
         <v>85</v>
       </c>
-      <c r="B6" s="0" t="n">
+      <c r="B6" s="1" t="n">
         <v>2174000000</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A7" s="0" t="s">
+      <c r="A7" s="1" t="s">
         <v>18</v>
       </c>
-      <c r="B7" s="0" t="n">
+      <c r="B7" s="1" t="n">
         <v>2236000000</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A8" s="0" t="s">
+      <c r="A8" s="1" t="s">
         <v>144</v>
       </c>
-      <c r="B8" s="0" t="n">
+      <c r="B8" s="1" t="n">
         <v>3000000</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A9" s="0" t="s">
+      <c r="A9" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="B9" s="0" t="n">
+      <c r="B9" s="1" t="n">
         <v>10694000000</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A10" s="0" t="s">
+      <c r="A10" s="1" t="s">
         <v>89</v>
       </c>
-      <c r="B10" s="0" t="n">
+      <c r="B10" s="1" t="n">
         <v>2408000000</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A11" s="0" t="s">
+      <c r="A11" s="1" t="s">
         <v>91</v>
       </c>
-      <c r="B11" s="0" t="n">
+      <c r="B11" s="1" t="n">
         <v>24000000</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A12" s="0" t="s">
+      <c r="A12" s="1" t="s">
         <v>96</v>
       </c>
-      <c r="B12" s="0" t="n">
+      <c r="B12" s="1" t="n">
         <v>35400000000</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A13" s="0" t="s">
+      <c r="A13" s="1" t="s">
         <v>58</v>
       </c>
-      <c r="B13" s="0" t="n">
+      <c r="B13" s="1" t="n">
         <v>2876000000</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A14" s="0" t="s">
+      <c r="A14" s="1" t="s">
         <v>99</v>
       </c>
-      <c r="B14" s="0" t="n">
+      <c r="B14" s="1" t="n">
         <v>2633000000</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A15" s="0" t="s">
+      <c r="A15" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="B15" s="0" t="n">
+      <c r="B15" s="1" t="n">
         <v>5474000000</v>
       </c>
     </row>
     <row r="16" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A16" s="0" t="s">
+      <c r="A16" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="B16" s="0" t="n">
+      <c r="B16" s="1" t="n">
         <v>13321000000</v>
       </c>
     </row>
     <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A17" s="0" t="s">
+      <c r="A17" s="1" t="s">
         <v>101</v>
       </c>
-      <c r="B17" s="0" t="n">
+      <c r="B17" s="1" t="n">
         <v>7000000</v>
       </c>
     </row>
     <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A18" s="0" t="s">
+      <c r="A18" s="1" t="s">
         <v>103</v>
       </c>
-      <c r="B18" s="0" t="n">
+      <c r="B18" s="1" t="n">
         <v>10000000</v>
       </c>
     </row>
     <row r="19" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A19" s="0" t="s">
+      <c r="A19" s="1" t="s">
         <v>145</v>
       </c>
-      <c r="B19" s="0" t="n">
+      <c r="B19" s="1" t="n">
         <v>1564000000</v>
       </c>
     </row>
     <row r="20" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A20" s="0" t="s">
+      <c r="A20" s="1" t="s">
         <v>139</v>
       </c>
-      <c r="B20" s="0" t="n">
+      <c r="B20" s="1" t="n">
         <v>499000000</v>
       </c>
     </row>
     <row r="21" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A21" s="0" t="s">
+      <c r="A21" s="1" t="s">
         <v>107</v>
       </c>
-      <c r="B21" s="0" t="n">
+      <c r="B21" s="1" t="n">
         <v>78000000</v>
       </c>
     </row>
     <row r="22" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A22" s="0" t="s">
+      <c r="A22" s="1" t="s">
         <v>20</v>
       </c>
-      <c r="B22" s="0" t="n">
+      <c r="B22" s="1" t="n">
         <v>51000000</v>
       </c>
     </row>
     <row r="23" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A23" s="0" t="s">
+      <c r="A23" s="1" t="s">
         <v>108</v>
       </c>
-      <c r="B23" s="0" t="n">
+      <c r="B23" s="1" t="n">
         <v>1350000000</v>
       </c>
     </row>
     <row r="24" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A24" s="0" t="s">
+      <c r="A24" s="1" t="s">
         <v>109</v>
       </c>
-      <c r="B24" s="0" t="n">
+      <c r="B24" s="1" t="n">
         <v>3000000</v>
       </c>
     </row>
     <row r="25" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A25" s="0" t="s">
+      <c r="A25" s="1" t="s">
         <v>111</v>
       </c>
-      <c r="B25" s="0" t="n">
+      <c r="B25" s="1" t="n">
         <v>6750000000</v>
       </c>
     </row>
     <row r="26" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A26" s="0" t="s">
+      <c r="A26" s="1" t="s">
         <v>112</v>
       </c>
-      <c r="B26" s="0" t="n">
+      <c r="B26" s="1" t="n">
         <v>6000000</v>
       </c>
     </row>
     <row r="27" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A27" s="0" t="s">
+      <c r="A27" s="1" t="s">
         <v>113</v>
       </c>
-      <c r="B27" s="0" t="n">
+      <c r="B27" s="1" t="n">
         <v>57000000</v>
       </c>
     </row>
     <row r="28" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A28" s="0" t="s">
+      <c r="A28" s="1" t="s">
         <v>146</v>
       </c>
-      <c r="B28" s="0" t="n">
+      <c r="B28" s="1" t="n">
         <v>332000000</v>
       </c>
     </row>
     <row r="29" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A29" s="0" t="s">
+      <c r="A29" s="1" t="s">
         <v>21</v>
       </c>
-      <c r="B29" s="0" t="n">
+      <c r="B29" s="1" t="n">
         <v>2857000000</v>
       </c>
     </row>
     <row r="30" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A30" s="0" t="s">
+      <c r="A30" s="1" t="s">
         <v>35</v>
       </c>
-      <c r="B30" s="0" t="n">
+      <c r="B30" s="1" t="n">
         <v>147000000</v>
       </c>
     </row>
     <row r="31" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A31" s="0" t="s">
+      <c r="A31" s="1" t="s">
         <v>27</v>
       </c>
-      <c r="B31" s="0" t="n">
+      <c r="B31" s="1" t="n">
         <v>5071000000</v>
       </c>
     </row>
     <row r="32" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A32" s="0" t="s">
+      <c r="A32" s="1" t="s">
         <v>55</v>
       </c>
-      <c r="B32" s="0" t="n">
+      <c r="B32" s="1" t="n">
         <v>33000000</v>
       </c>
     </row>
     <row r="33" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A33" s="0" t="s">
+      <c r="A33" s="1" t="s">
         <v>117</v>
       </c>
-      <c r="B33" s="0" t="n">
+      <c r="B33" s="1" t="n">
         <v>280000000</v>
       </c>
     </row>
     <row r="34" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A34" s="0" t="s">
+      <c r="A34" s="1" t="s">
         <v>11</v>
       </c>
-      <c r="B34" s="0" t="n">
+      <c r="B34" s="1" t="n">
         <v>90447000000</v>
       </c>
     </row>
     <row r="35" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A35" s="0" t="s">
+      <c r="A35" s="1" t="s">
         <v>118</v>
       </c>
-      <c r="B35" s="0" t="n">
+      <c r="B35" s="1" t="n">
         <v>7112000000</v>
       </c>
     </row>
     <row r="36" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A36" s="0" t="s">
+      <c r="A36" s="1" t="s">
         <v>59</v>
       </c>
-      <c r="B36" s="0" t="n">
+      <c r="B36" s="1" t="n">
         <v>135000000</v>
       </c>
     </row>
     <row r="37" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A37" s="0" t="s">
+      <c r="A37" s="1" t="s">
         <v>136</v>
       </c>
-      <c r="B37" s="0" t="n">
+      <c r="B37" s="1" t="n">
         <v>315000000</v>
       </c>
     </row>
     <row r="38" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A38" s="0" t="s">
+      <c r="A38" s="1" t="s">
         <v>60</v>
       </c>
-      <c r="B38" s="0" t="n">
+      <c r="B38" s="1" t="n">
         <v>319000000</v>
       </c>
     </row>
     <row r="39" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A39" s="0" t="s">
+      <c r="A39" s="1" t="s">
         <v>123</v>
       </c>
-      <c r="B39" s="0" t="n">
+      <c r="B39" s="1" t="n">
         <v>1063000000</v>
       </c>
     </row>
     <row r="40" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A40" s="0" t="s">
+      <c r="A40" s="1" t="s">
         <v>23</v>
       </c>
-      <c r="B40" s="0" t="n">
+      <c r="B40" s="1" t="n">
         <v>10975000000</v>
       </c>
     </row>
     <row r="41" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A41" s="0" t="s">
+      <c r="A41" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="B41" s="0" t="n">
+      <c r="B41" s="1" t="n">
         <v>29867000000</v>
       </c>
     </row>
     <row r="42" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A42" s="0" t="s">
+      <c r="A42" s="1" t="s">
         <v>53</v>
       </c>
-      <c r="B42" s="0" t="n">
+      <c r="B42" s="1" t="n">
         <v>2336000000</v>
       </c>
     </row>
     <row r="43" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A43" s="0" t="s">
+      <c r="A43" s="1" t="s">
         <v>13</v>
       </c>
-      <c r="B43" s="0" t="n">
+      <c r="B43" s="1" t="n">
         <v>244000000</v>
       </c>
     </row>
@@ -6048,10 +6060,10 @@
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
   <dimension ref="A1:B23"/>
-  <sheetFormatPr defaultColWidth="8.5390625" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <sheetFormatPr defaultColWidth="8.54296875" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="32"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="0" width="20"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="32"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="1" width="20"/>
   </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -6063,170 +6075,170 @@
       </c>
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A2" s="0" t="s">
+      <c r="A2" s="1" t="s">
         <v>54</v>
       </c>
-      <c r="B2" s="0" t="n">
+      <c r="B2" s="1" t="n">
         <v>7000</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A3" s="0" t="s">
+      <c r="A3" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="B3" s="0" t="n">
+      <c r="B3" s="1" t="n">
         <v>156000</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A4" s="0" t="s">
+      <c r="A4" s="1" t="s">
         <v>18</v>
       </c>
-      <c r="B4" s="0" t="n">
+      <c r="B4" s="1" t="n">
         <v>282000</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A5" s="0" t="s">
+      <c r="A5" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="B5" s="0" t="n">
+      <c r="B5" s="1" t="n">
         <v>56000</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A6" s="0" t="s">
+      <c r="A6" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="B6" s="0" t="n">
+      <c r="B6" s="1" t="n">
         <v>2000</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A7" s="0" t="s">
+      <c r="A7" s="1" t="s">
         <v>101</v>
       </c>
-      <c r="B7" s="0" t="n">
+      <c r="B7" s="1" t="n">
         <v>5000</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A8" s="0" t="s">
+      <c r="A8" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="B8" s="0" t="n">
+      <c r="B8" s="1" t="n">
         <v>316000</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A9" s="3" t="s">
+      <c r="A9" s="1" t="s">
         <v>108</v>
       </c>
-      <c r="B9" s="3" t="n">
+      <c r="B9" s="1" t="n">
         <v>8000</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A10" s="3" t="s">
+      <c r="A10" s="1" t="s">
         <v>134</v>
       </c>
-      <c r="B10" s="3" t="n">
+      <c r="B10" s="1" t="n">
         <v>12000</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A11" s="3" t="s">
+      <c r="A11" s="1" t="s">
         <v>112</v>
       </c>
-      <c r="B11" s="3" t="n">
+      <c r="B11" s="1" t="n">
         <v>15000</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A12" s="3" t="s">
+      <c r="A12" s="1" t="s">
         <v>26</v>
       </c>
-      <c r="B12" s="3" t="n">
+      <c r="B12" s="1" t="n">
         <v>14000</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A13" s="0" t="s">
+      <c r="A13" s="1" t="s">
         <v>55</v>
       </c>
-      <c r="B13" s="0" t="n">
+      <c r="B13" s="1" t="n">
         <v>4000</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A14" s="0" t="s">
+      <c r="A14" s="1" t="s">
         <v>11</v>
       </c>
-      <c r="B14" s="0" t="n">
+      <c r="B14" s="1" t="n">
         <v>21000</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A15" s="0" t="s">
+      <c r="A15" s="1" t="s">
         <v>59</v>
       </c>
-      <c r="B15" s="0" t="n">
+      <c r="B15" s="1" t="n">
         <v>9000</v>
       </c>
     </row>
     <row r="16" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A16" s="0" t="s">
+      <c r="A16" s="1" t="s">
         <v>136</v>
       </c>
-      <c r="B16" s="0" t="n">
+      <c r="B16" s="1" t="n">
         <v>2000</v>
       </c>
     </row>
     <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A17" s="0" t="s">
+      <c r="A17" s="1" t="s">
         <v>29</v>
       </c>
-      <c r="B17" s="0" t="n">
+      <c r="B17" s="1" t="n">
         <v>166000</v>
       </c>
     </row>
     <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A18" s="0" t="s">
+      <c r="A18" s="1" t="s">
         <v>60</v>
       </c>
-      <c r="B18" s="0" t="n">
+      <c r="B18" s="1" t="n">
         <v>19000</v>
       </c>
     </row>
     <row r="19" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A19" s="0" t="s">
+      <c r="A19" s="1" t="s">
         <v>43</v>
       </c>
-      <c r="B19" s="0" t="n">
+      <c r="B19" s="1" t="n">
         <v>38000</v>
       </c>
     </row>
     <row r="20" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A20" s="0" t="s">
+      <c r="A20" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="B20" s="0" t="n">
+      <c r="B20" s="1" t="n">
         <v>9000</v>
       </c>
     </row>
     <row r="21" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A21" s="0" t="s">
+      <c r="A21" s="1" t="s">
         <v>53</v>
       </c>
-      <c r="B21" s="0" t="n">
+      <c r="B21" s="1" t="n">
         <v>45000</v>
       </c>
     </row>
     <row r="22" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A22" s="0" t="s">
+      <c r="A22" s="1" t="s">
         <v>44</v>
       </c>
-      <c r="B22" s="0" t="n">
+      <c r="B22" s="1" t="n">
         <v>27000</v>
       </c>
     </row>
